--- a/www/download/COUNTRY.LVA.rpO1.xlsx
+++ b/www/download/COUNTRY.LVA.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Letônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.52728173079657</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.550724544072686</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.58083123364813</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.589615463491515</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.585058794082016</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.605770394130792</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.627829148300881</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.617733968152981</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.571213110542708</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.540099751885512</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.563821768266915</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.559922910932404</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.513073138936895</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.478537591225876</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.504283874684475</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.04380310418494</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>1.93977292043054</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>1.85374015298091</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.83128086251183</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>1.93346617116337</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>1.89941135367234</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>1.83169748716191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>1.91036372688989</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.22009535294332</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1.97183448272827</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1.98733223977999</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1.89851911791254</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1.86345158277339</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1.70139550915943</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>1.71785133071052</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>4.34104353432228</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>4.17991943953952</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4.01907499714247</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>3.97596795673717</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>4.14314621884333</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>4.05652805814889</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>3.89570791184148</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>3.96832328596602</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>3.99955068512572</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>3.93154231900156</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>3.91174875411893</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>3.83037585617222</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>3.73939741906442</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>3.90720391168235</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>3.92596854756529</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1514.59</t>
+          <t>4.96242418401891</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1493.457</t>
+          <t>4.7353884166364</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1534.138</t>
+          <t>4.5412078751961</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1582.666</t>
+          <t>4.47779727324192</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>4.70505161374668</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1526.578</t>
+          <t>4.66524473479629</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1501.692</t>
+          <t>4.46205515109309</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1489.298</t>
+          <t>4.55538142290059</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1523.524</t>
+          <t>3.29363015566682</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1544.045</t>
+          <t>4.55006143954577</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1592.962</t>
+          <t>4.48478197009891</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1664.197</t>
+          <t>4.20158511032547</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1737.5</t>
+          <t>4.13329970810126</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1686.662</t>
+          <t>4.01066553300597</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1417.767</t>
+          <t>4.20611993175229</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1336.081</t>
+          <t>230750390596.673</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1323.147</t>
+          <t>235204618866.836</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1305.686</t>
+          <t>283827950416.235</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1371.662</t>
+          <t>330019200842.025</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1370.661</t>
+          <t>342388975063.829</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1362.726</t>
+          <t>386375695032.718</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1341.531</t>
+          <t>431292326983.38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1351.454</t>
+          <t>454620397525.955</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1384.114</t>
+          <t>547225919263.863</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1399.416</t>
+          <t>559373698495.177</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1456.632</t>
+          <t>628488224103.754</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1522.637</t>
+          <t>702610762987.766</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1594.493</t>
+          <t>754735163280.957</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1565.39</t>
+          <t>683071724649.961</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1306.652</t>
+          <t>433634985320.837</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>38975170373.9637</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41962906355.4264</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>45405819106.234</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>54036547812.6367</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>62012924629.9712</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>71503860152.9333</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>77749005459.7537</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>81392644608.6701</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>95434450604.0125</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>96479225488.3726</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>106364289278.934</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>118628861837.181</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>137000208885.96</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>130230548696.011</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>88582905765.021</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>954029551.66922</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>867490596.399121</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>900527610.402965</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>987386361.785931</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>1066010619.67542</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>1147270385.76982</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>1139812427.49859</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>1200243206.64582</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>1044445017.01506</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>847405336.519449</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>791089430.478601</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.76</t>
+          <t>685197889.8145</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.08</t>
+          <t>524078064.252873</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>418645921.731409</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>52.95</t>
+          <t>376619040.304294</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>5588.99670385843</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>6328.32546294936</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>7381.83142699275</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>7497.23374100324</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>7581.54931727301</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>7590.16027034891</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>7882.05190520486</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>8616.55921637493</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>10557.1109380138</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>12666.2966714296</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16151.6882860868</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>20773.5520772958</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>31224.1884250036</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>39034.0517231036</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>25431.9017967692</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>10373.7720505159</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>11876.8301017459</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>14031.0222868052</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>14805.5501350679</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>14318.1941880731</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>14246.7233918414</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>15037.6112106513</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>16572.619379234</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>20960.1979860677</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>25751.6369477021</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>32387.547558424</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>41999.5533667834</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>60165.0607456471</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>72547.5741443617</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>47948.9062240063</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>65.77</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>67.63</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.73</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66.71</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>64.09</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>63.32</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>1121.04857534057</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>1444.31150787025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>1548.1476282494</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>1637.76013295514</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>1780.26888633514</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>1952.37820152961</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>2012.9015483561</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>2023.94165044062</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>2328.8331605944</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>2717.19442423764</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>3191.49660903645</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>4062.03131246715</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>6012.11142013061</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>7247.18925429016</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>6335.51879334942</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.52728173079657</t>
+          <t>47212.1423164831</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.550724544072686</t>
+          <t>51669.0798975828</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.58083123364813</t>
+          <t>56758.8861823652</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.589615463491515</t>
+          <t>65964.066949128</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.585058794082016</t>
+          <t>76119.6337539362</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.605770394130792</t>
+          <t>89458.1010295676</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.627829148300881</t>
+          <t>96220.9650959445</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.617733968152981</t>
+          <t>96674.3880834725</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.571213110542708</t>
+          <t>110201.444115488</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.540099751885512</t>
+          <t>110215.66200713</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.563821768266915</t>
+          <t>116959.381934271</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.559922910932404</t>
+          <t>124728.064175356</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.513073138936895</t>
+          <t>137716.333821833</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.478537591225876</t>
+          <t>128762.438653934</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.504283874684475</t>
+          <t>102348.822374374</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>11242440588.9738</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>13216379879.083</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6698104277.47274</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11058328711.6147</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>18155425286.9732</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>26316791068.9757</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>33730584317.611</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>39030591659.6062</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>39210410891.1173</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>40361671152.112</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>48025093724.3834</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>35387989155.6322</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>27809197576.2186</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>15281416890.1584</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>31228838122.3966</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-5474074651.56258</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-5963402429.08227</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-9159305660.75091</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-7943003088.79229</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-4090994754.13697</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-5555930162.27118</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1980752046.2367</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6169261469.30457</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7880011936.13663</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>11307279599.4646</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>11061096760.5279</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4712651739.58269</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-86766446.2324416</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-14020371820.3874</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2074604965.61922</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16716515240.5364</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19179782308.1653</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>15857409938.2236</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19001331800.4069</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>22246420041.1102</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>31872721231.2469</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>31749832271.3743</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>32861330190.3016</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>31330398954.9806</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>29054391552.6474</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36963996963.8554</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>30675337416.0495</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>27895964022.451</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>29301788710.5458</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>29154233156.7774</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>211627.372223866</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>224733.777722766</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>240503.202436935</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>278003.46389738</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>330901.930503218</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>381266.502242911</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>399051.36088391</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>406625.232445244</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>476516.543922599</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>462764.783464236</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>494407.547105273</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>516693.570538383</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>557819.900569161</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>508580.084092753</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>395745.178764829</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>204483.092567595</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>225921.139971756</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>248156.955880757</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>292129.994560234</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>347592.310964938</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>418575.908410949</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>455464.359446859</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>459763.479547164</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>531357.39060857</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>539738.186449906</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>588114.912848242</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>630059.153627879</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>706159.512998225</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>670587.937196472</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>538481.35630473</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>204.38</t>
+          <t>1908.48447905302</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>193.98</t>
+          <t>2300.41360112393</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>185.37</t>
+          <t>2550.0382548719</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>183.13</t>
+          <t>2815.45629405511</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>193.35</t>
+          <t>2697.9583132818</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>3038.65417083858</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>183.17</t>
+          <t>3221.52339949215</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>191.04</t>
+          <t>3534.72074837867</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>222.01</t>
+          <t>4266.44099066123</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>197.18</t>
+          <t>5188.17464186705</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>198.73</t>
+          <t>6561.42246610176</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>189.85</t>
+          <t>7450.33470243026</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>186.35</t>
+          <t>10005.0742839654</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>170.14</t>
+          <t>12075.8027705712</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>171.79</t>
+          <t>9650.08103198093</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>434.1</t>
+          <t>51915889835.7125</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>417.99</t>
+          <t>55294676111.1043</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>401.91</t>
+          <t>71347927303.7612</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>397.6</t>
+          <t>86877723217.6603</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>414.31</t>
+          <t>86086623241.6829</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>405.65</t>
+          <t>99924904440.9921</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>389.57</t>
+          <t>108893913028.975</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>396.83</t>
+          <t>112663556340.731</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>399.96</t>
+          <t>133340495369.957</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>393.15</t>
+          <t>129084348306.94</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>391.17</t>
+          <t>146960336571.992</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>383.04</t>
+          <t>144295033239.84</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>373.94</t>
+          <t>148140165254.759</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>390.72</t>
+          <t>142145772211.199</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>392.6</t>
+          <t>98191925749.8992</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>496.24</t>
+          <t>2022.77709700093</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>473.54</t>
+          <t>2566.32479052205</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>454.12</t>
+          <t>2864.46573141088</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>447.78</t>
+          <t>3445.58965575006</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>470.51</t>
+          <t>3166.02231831759</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>466.52</t>
+          <t>3394.63803948598</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>446.21</t>
+          <t>3832.06682658459</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>455.54</t>
+          <t>4288.25100352991</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>329.36</t>
+          <t>5449.88611595084</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>455.01</t>
+          <t>7141.45479756449</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>448.48</t>
+          <t>8617.06183088683</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>11386.6674442325</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>413.33</t>
+          <t>15338.799790818</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>401.07</t>
+          <t>16280.5359341653</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>420.61</t>
+          <t>10057.2603942484</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>198294.547</t>
+          <t>67329661703.0166</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>214912.014</t>
+          <t>77165081003.16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>246419.374</t>
+          <t>88527672326.9027</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>289176.62</t>
+          <t>121566875524.852</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>337993.135</t>
+          <t>123141160715.125</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>394047.36</t>
+          <t>142440186573.271</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>434103.081</t>
+          <t>172499924917.539</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>450993.779</t>
+          <t>187242112964.753</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>531410.526</t>
+          <t>225139149628.209</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>546467.455</t>
+          <t>240642118529.657</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>606941.767</t>
+          <t>261595979510.528</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>680022.845</t>
+          <t>288428193971.615</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>789274.488</t>
+          <t>284440518626.36</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>751432.917</t>
+          <t>220643582407.963</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>514392.921</t>
+          <t>135444501380.842</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>174705.33</t>
+          <t>-114.29261794791</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>182516.942</t>
+          <t>-265.911189398116</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>192397.097</t>
+          <t>-314.42747653898</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>227735.314</t>
+          <t>-630.133361694954</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>269578.234</t>
+          <t>-468.064005035782</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>304746.315</t>
+          <t>-355.983868647399</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>322443.725</t>
+          <t>-610.543427092448</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>342348.203</t>
+          <t>-753.530255151241</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>412663.327</t>
+          <t>-1183.44512528962</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>405089.323</t>
+          <t>-1953.28015569744</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>449620.257</t>
+          <t>-2055.63936478507</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>491427.255</t>
+          <t>-3936.33274180224</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>554919.237</t>
+          <t>-5333.72550685266</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>514378.759</t>
+          <t>-4204.73316359411</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>342517.452</t>
+          <t>-407.179362267443</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>230750.391</t>
+          <t>-15413771867.3041</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>235204.619</t>
+          <t>-21870404892.0557</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>283827.95</t>
+          <t>-17179745023.1415</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>330019.201</t>
+          <t>-34689152307.1914</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>342388.975</t>
+          <t>-37054537473.4425</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>386375.695</t>
+          <t>-42515282132.2794</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>431292.327</t>
+          <t>-63606011888.5634</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>454620.398</t>
+          <t>-74578556624.0221</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>547225.919</t>
+          <t>-91798654258.2523</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>559373.698</t>
+          <t>-111557770222.718</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>628488.224</t>
+          <t>-114635642938.535</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>702610.763</t>
+          <t>-144133160731.775</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>754735.163</t>
+          <t>-136300353371.601</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>683071.725</t>
+          <t>-78497810196.7634</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>433634.985</t>
+          <t>-37252575630.9431</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2332.07772</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2492.55037</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2630.89855</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2668.99535</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2710.47713</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2866.10153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3016.74428</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3282.15748</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>3893.64277</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4725.97942</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>5463.07347</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>6616.26715</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>10108.11168</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>12004.2816</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>8913.43179</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>124319.598</t>
+          <t>0.0528500374930362</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>125323.96</t>
+          <t>0.0373470313312112</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>149324.122</t>
+          <t>0.0450043728146852</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>167115.107</t>
+          <t>0.0524546865449264</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>181296.528</t>
+          <t>0.0561188651672783</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>205847.574</t>
+          <t>0.0675451840837602</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>226064.397</t>
+          <t>0.0802475008263748</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>236369.61</t>
+          <t>0.107299706270236</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>275623.577</t>
+          <t>0.106912112175635</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>275135.644</t>
+          <t>0.115760913705338</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>313427.433</t>
+          <t>0.100539471116933</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>347520.869</t>
+          <t>0.0855227314032824</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>391689.008</t>
+          <t>0.0667745333620337</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>367525.136</t>
+          <t>0.0492391117297828</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>229998.205</t>
+          <t>0.0490343356879938</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2172.24091164139</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2606.77053933799</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2747.62816097584</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2945.32700799828</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3174.87626423622</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3233.40231233089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3291.34126466962</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3580.18221014853</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>4422.86729020185</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5410.66785573386</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6706.90624696575</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>8739.59498049103</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>13482.0947985381</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>17141.6124501607</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>12000.9795323206</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>38975.17</t>
+          <t>2433.76641698823</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>41962.906</t>
+          <t>2911.4719976861</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45405.819</t>
+          <t>3175.20318680375</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54036.548</t>
+          <t>3303.52479953617</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>62012.925</t>
+          <t>3550.50419662563</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>71503.86</t>
+          <t>3576.08119780887</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>77749.005</t>
+          <t>3665.28545269562</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>81392.645</t>
+          <t>3949.85019166349</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>95434.451</t>
+          <t>4870.61141889268</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>96479.225</t>
+          <t>5954.6074726428</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>106364.289</t>
+          <t>7378.38734092036</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>118628.862</t>
+          <t>9583.26873796141</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>137000.209</t>
+          <t>14776.8212147021</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>130230.549</t>
+          <t>18752.5633268763</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>88582.906</t>
+          <t>13108.3148496071</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>15264.8048315482</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>18050.3989317155</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>17947.6371834533</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>18348.5717083518</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>20587.7991936461</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>22089.2165873931</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>22571.0565475078</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>22606.0018448414</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>26250.0880714291</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>31645.6417443656</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>36512.6535803401</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>45847.9839831326</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>69852.39447318</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>88187.4801613657</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>80206.6576789869</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>954.03</t>
+          <t>2433.76641698823</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>867.491</t>
+          <t>2592.69569434647</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>900.528</t>
+          <t>2962.10341224479</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>987.386</t>
+          <t>3082.18532629085</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1066.011</t>
+          <t>2999.67412382246</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1147.27</t>
+          <t>2922.57579889783</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1139.812</t>
+          <t>3014.19995352898</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1200.243</t>
+          <t>3089.64437618504</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1044.445</t>
+          <t>3386.25644271139</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>847.405</t>
+          <t>3592.27578976512</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>791.089</t>
+          <t>4288.50259190604</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>685.198</t>
+          <t>5005.89338127128</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>524.078</t>
+          <t>5629.21264710926</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>418.646</t>
+          <t>5904.58436836143</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>376.619</t>
+          <t>4455.41855739918</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2172.24091164139</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2316.41683544819</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2452.95822587968</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2621.59149193219</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2586.54519511877</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2588.61826112566</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2645.59427708177</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2741.38897718325</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>3018.49067000157</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>3226.38869144186</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3839.85275620047</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>4505.73183312841</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>5068.99511408834</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>5286.83672339898</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3965.4191451397</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1927.79408301177</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2118.4403223139</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2355.86978319625</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2600.22871046383</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2935.63281337437</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3444.39840219113</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3824.17242730438</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4449.55900833651</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5135.28552110732</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6380.5228273572</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6862.45948907964</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>7983.07613203859</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>10676.4724652979</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>11589.4624431237</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10268.3989703929</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>174705329678.288</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>182516942205.561</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>192397096539.825</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>227735313539.032</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>269578234474.19</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>304746315242.759</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>322443725285.322</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>342348202967.232</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>412663327036.971</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>405089322868.065</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>449620256984.141</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>491427254939.056</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>554919237086.201</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>514378759051.553</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>342517452220.959</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>198294547204.603</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>214912013944.869</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>246419374382.138</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>289176620012.836</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>337993134933.226</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>394047360178.067</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>434103080988.801</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>450993778526.976</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>531410526347.63</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>546467455424.499</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>606941767291.142</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>680022844510.57</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>789274487678.116</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>751432916750.966</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>514392921369.617</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>124319598134.481</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>125323959829.946</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>149324122035.769</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>167115106508.023</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>181296528461.619</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>205847574154.856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>226064396796.727</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>236369609813.325</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>275623576726.958</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>275135643987.361</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>313427432839.379</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>347520868794.246</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>391689007826.115</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>367525135678.825</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>229998204980.984</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>969735.662321586</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>951270.049238141</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>992998.054427078</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>989890.204352882</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>972383.807901089</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>941400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>953100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>980925.625</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1000100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1012467.65402844</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1032012.20379147</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1079300</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1117700</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1120558.35643642</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>955265.981536636</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>825532.764700584</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>812147.350767697</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>799977.275106245</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>819181.568266706</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>814677.128248328</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>799300</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>808025.625</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>841925.625</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>866000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>875367.654028436</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>909412.203791469</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>951100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>994800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1011401.69491525</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>865500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1514590032.04503</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1493457060.44326</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1534138017.54915</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1582666354.38879</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1567999923.67959</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1526577820.99134</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1501692005.47824</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1489298335.19792</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1523523547.78141</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1544044635.48969</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1592961685.28713</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1664196888.97509</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1737499758.92836</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1686661984.74619</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1417766576.16466</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1336081307.41044</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1323146895.9235</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1305686489.00979</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1371662037.92692</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1370660915.40396</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1362726259.10289</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1341531498.4363</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1351453782.44377</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1384113728.95087</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1399416320.30675</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1456632329.86547</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1522636753.83629</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1594493377.14699</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1565390254.85935</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1306652451.44424</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.337479986825909</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.330003801342482</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.320238755438438</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.308911232579517</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.302417281122463</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.304864401943408</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.299503042270685</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.301891604431734</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.252825706415686</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.307042313712825</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.286994506473726</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.29601822873383</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.316971631715025</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.377103430037909</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.377178843101775</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.552308389577755</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.56085972469758</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.560053731319587</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.558693728344203</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.579239365217289</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.581020229331219</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.587151450348968</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.587498722179865</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.604007867943318</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.59501943934149</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.60436958624526</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.597569119132053</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570767725225988</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.519722552787632</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.529510388783344</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.110211623596336</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.109136473959937</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.119707513241975</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.13239503907628</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.118343353660248</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.114115368725373</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.113345507380347</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.110609673388401</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.143166425640996</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0979382469456849</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.108635907281014</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.106412652134116</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.112260643058987</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.103174017174459</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0933107681148805</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.221402598356645</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.217783825319958</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.20956731176511</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.201145532179456</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.196767345891568</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.19894241748371</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.19874063203842</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.204052674995567</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.187227688565911</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.211098684816096</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.197425017902899</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.201618232029366</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.218079798267664</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.24652483085632</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.24740962224875</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.636134326408564</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.643016147857893</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.639034254055017</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.633464354881649</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.654347644429622</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.656315381336742</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.658893951101241</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.65766276242967</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.676271119393828</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.665136407929561</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.667321460850943</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.667125102185177</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.640875307759502</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.622209834050845</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.633193878189163</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.14246307523479</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.139200026822149</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.151398434179873</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.165390112938895</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.14888500967881</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.144742201179548</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.142365416860339</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.138284562574763</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.13650119204026</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.123764907254343</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.135253521246158</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.131256665785457</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.141044893972834</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.131265335092835</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.119396499562087</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9059.74019</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>10317.35837</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11517.97645</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>12828.85861</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>13434.56323</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14948.72866</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15967.24185</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>17667.63885</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>21866.44317</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>27839.86056</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>32433.11932</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>41785.92693</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>57759.80196</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>67537.84991</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>50783.69802</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4361.5605</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5029.91232</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5531.07297</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5903.75351</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6486.13701</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7020.4796</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7489.45788</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>8399.4092</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10005.89694</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>12335.1303</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>14240.84683</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>17566.34487</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>25453.29368</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>30342.02577</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>23376.71382</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8048.84982002744</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8415.75012239713</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8905.44438457186</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9345.92642870107</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>9696.90119167796</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10104.4440922637</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10583.1538767944</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11154.6606234035</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11824.0170336517</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>12744.3098045286</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>13968.9255708682</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>15426.5326394851</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>16960.8247896626</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>18090.417026717</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>18394.9787628832</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
